--- a/StructureDefinition-access-submission-status-out.xlsx
+++ b/StructureDefinition-access-submission-status-out.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$30</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="178">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T23:16:42-05:00</t>
+    <t>2026-03-06T16:03:26-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This is the profile for the $submission-status operation output parameters (generic for all APIs).</t>
+    <t>This is the profile for the $submission-status operation output parameters (generic for all APIs). When the result indicates a validation error, the optional 'issues' parameter MAY contain an OperationOutcome resource with detailed validation error information to help implementers understand and correct the submission.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -533,6 +533,43 @@
   </si>
   <si>
     <t>Parameters.parameter:result.part</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:issues</t>
+  </si>
+  <si>
+    <t>issues</t>
+  </si>
+  <si>
+    <t>Provides more result context</t>
+  </si>
+  <si>
+    <t>When present, contains an OperationOutcome resource with detailed information about submission errors, warnings, or informational messages. This parameter is typically included when the result code indicates a validation error to provide structured, parseable details about what validation checks failed and how to correct the submission.</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:issues.id</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:issues.extension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:issues.modifierExtension</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:issues.name</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:issues.value[x]</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:issues.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OperationOutcome
+</t>
+  </si>
+  <si>
+    <t>Parameters.parameter:issues.part</t>
   </si>
 </sst>
 </file>
@@ -849,10 +886,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL22"/>
+  <dimension ref="A1:AL30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="37.1484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="37.5234375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="32.28515625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.79296875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="17.796875" customWidth="true" bestFit="true" hidden="true"/>
@@ -3261,8 +3298,868 @@
         <v>75</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="D23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
+      <c r="A24" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" hidden="true">
+      <c r="A25" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="P26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL22">
+  <autoFilter ref="A1:AL30">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -3272,7 +4169,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI21">
+  <conditionalFormatting sqref="A2:AI29">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-access-submission-status-out.xlsx
+++ b/StructureDefinition-access-submission-status-out.xlsx
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://globalalliantinc.com/access/StructureDefinition/access-submission-status-out</t>
+    <t>https://dsacms.github.io/cmmi-access-model/StructureDefinition/access-submission-status-out</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T16:03:26-05:00</t>
+    <t>2026-03-12T23:55:37-07:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-submission-status-out.xlsx
+++ b/StructureDefinition-access-submission-status-out.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="177">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.1</t>
+    <t>0.9.6</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T23:55:37-07:00</t>
+    <t>2026-04-24T13:45:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -349,9 +349,6 @@
   </si>
   <si>
     <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
@@ -1539,29 +1536,27 @@
       <c r="X6" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Y6" s="2"/>
+      <c r="Z6" t="s" s="2">
         <v>109</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AA6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE6" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF6" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="AA6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE6" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF6" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -1584,10 +1579,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1610,13 +1605,13 @@
         <v>85</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L7" t="s" s="2">
+      <c r="M7" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1655,17 +1650,17 @@
         <v>75</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AC7" s="2"/>
       <c r="AD7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -1677,7 +1672,7 @@
         <v>75</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>75</v>
@@ -1688,10 +1683,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1714,13 +1709,13 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1771,7 +1766,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>76</v>
@@ -1794,14 +1789,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1820,16 +1815,16 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1879,7 +1874,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>76</v>
@@ -1891,7 +1886,7 @@
         <v>75</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>75</v>
@@ -1902,14 +1897,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -1928,19 +1923,19 @@
         <v>85</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="O10" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>75</v>
@@ -1989,7 +1984,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -2001,21 +1996,21 @@
         <v>75</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2038,13 +2033,13 @@
         <v>85</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2095,7 +2090,7 @@
         <v>75</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>84</v>
@@ -2118,10 +2113,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2144,13 +2139,13 @@
         <v>85</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2201,7 +2196,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2210,7 +2205,7 @@
         <v>84</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>96</v>
@@ -2224,10 +2219,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2250,16 +2245,16 @@
         <v>85</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2309,7 +2304,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2318,7 +2313,7 @@
         <v>84</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>75</v>
@@ -2332,10 +2327,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2361,13 +2356,13 @@
         <v>75</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2417,7 +2412,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2440,13 +2435,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C15" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>75</v>
@@ -2468,13 +2463,13 @@
         <v>85</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2525,7 +2520,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -2537,7 +2532,7 @@
         <v>75</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>75</v>
@@ -2548,10 +2543,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2574,13 +2569,13 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2631,7 +2626,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2654,14 +2649,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2680,16 +2675,16 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2739,7 +2734,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -2751,7 +2746,7 @@
         <v>75</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>75</v>
@@ -2762,14 +2757,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -2788,19 +2783,19 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="O18" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>75</v>
@@ -2849,7 +2844,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -2861,21 +2856,21 @@
         <v>75</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2898,13 +2893,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2913,7 +2908,7 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="S19" t="s" s="2">
         <v>75</v>
@@ -2955,7 +2950,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>84</v>
@@ -2978,10 +2973,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3004,13 +2999,13 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3061,7 +3056,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3070,7 +3065,7 @@
         <v>84</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>96</v>
@@ -3084,10 +3079,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3110,16 +3105,16 @@
         <v>85</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>148</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3169,7 +3164,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3178,7 +3173,7 @@
         <v>84</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>75</v>
@@ -3192,10 +3187,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3221,13 +3216,13 @@
         <v>78</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3277,7 +3272,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3300,13 +3295,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>75</v>
@@ -3328,13 +3323,13 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3385,7 +3380,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3397,7 +3392,7 @@
         <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>75</v>
@@ -3408,10 +3403,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3434,13 +3429,13 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>120</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>122</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3491,7 +3486,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3514,14 +3509,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3540,16 +3535,16 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3599,7 +3594,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3611,7 +3606,7 @@
         <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>75</v>
@@ -3622,14 +3617,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -3648,19 +3643,19 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="O26" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -3709,7 +3704,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3721,21 +3716,21 @@
         <v>75</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3758,13 +3753,13 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>140</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>141</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3773,7 +3768,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>75</v>
@@ -3815,7 +3810,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>84</v>
@@ -3838,10 +3833,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3864,13 +3859,13 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3921,7 +3916,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -3930,7 +3925,7 @@
         <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>96</v>
@@ -3944,10 +3939,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3970,16 +3965,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4029,7 +4024,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4038,7 +4033,7 @@
         <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>75</v>
@@ -4052,10 +4047,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4081,13 +4076,13 @@
         <v>78</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4137,7 +4132,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>

--- a/StructureDefinition-access-submission-status-out.xlsx
+++ b/StructureDefinition-access-submission-status-out.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.6</t>
+    <t>0.9.8</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:45:33-04:00</t>
+    <t>2026-05-18T15:59:44-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-submission-status-out.xlsx
+++ b/StructureDefinition-access-submission-status-out.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T15:59:44-04:00</t>
+    <t>2026-05-20T09:30:43-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-submission-status-out.xlsx
+++ b/StructureDefinition-access-submission-status-out.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.8</t>
+    <t>0.9.11</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T09:30:43-04:00</t>
+    <t>2026-06-04T22:54:52-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-submission-status-out.xlsx
+++ b/StructureDefinition-access-submission-status-out.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T22:54:52-04:00</t>
+    <t>2026-06-04T23:05:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-access-submission-status-out.xlsx
+++ b/StructureDefinition-access-submission-status-out.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.11</t>
+    <t>0.9.12</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T23:05:21-04:00</t>
+    <t>2026-06-10T23:08:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
